--- a/asphalt-plant/equipment/equipment.xlsx
+++ b/asphalt-plant/equipment/equipment.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-04-28T15:04:39</t>
+          <t>generated 2026-04-29T04:50:04</t>
         </is>
       </c>
     </row>

--- a/asphalt-plant/equipment/equipment.xlsx
+++ b/asphalt-plant/equipment/equipment.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-04-29T04:50:04</t>
+          <t>generated 2026-05-26T04:45:24</t>
         </is>
       </c>
     </row>

--- a/asphalt-plant/equipment/equipment.xlsx
+++ b/asphalt-plant/equipment/equipment.xlsx
@@ -484,7 +484,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-05-26T04:45:24</t>
+          <t>generated 2026-06-11T20:42:38</t>
         </is>
       </c>
     </row>
